--- a/extenbooks/XS1402.xlsx
+++ b/extenbooks/XS1402.xlsx
@@ -1253,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1359,121 +1359,130 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Productive labor share = L_p / L, where L_p is total productive full-time equivalent employment and L is total employment. Calculated using the SM (Simon Mohun) approximation: for each productive SIC division i, L_p^i = (L_pn^i / L^i)_BLS × (L^i)_NIPA, where BLS production worker ratios are applied to NIPA total employment. For Services divisions the SM approximation uses division-level BLS ratios weighted by a factor alpha^{s,j} = geometric mean of division BLS ratio / geometric mean of aggregate Services BLS ratio (first 5 years available).</t>
+          <t>STUDY ANCHOR (Mohun 2005 Figure 2, L_p/L, and Table 2, Services productive labour 1988). Figure 2 SM: ~0.45 (1964) -&gt; ~0.38 (2001); ST: ~0.45 (1964) -&gt; ~0.36 (2001). Table 2 Total productive services 1988 (thousands ftes): Benchmark 15,543; ST 14,170; SM 15,313. NOTE: series XS1402-A is a book-period (1948-1989) RECONSTRUCTION; its values run 0.566 (1948) -&gt; 0.525 (1989), and over the overlapping 1964-1989 sit ~0.55-&gt;0.52 — well ABOVE Mohun published SM L_p/L (~0.45-&gt;~0.40). No year-matched external anchor exists; the single 1948 refval is the series own output (tautological), documented as a divergence.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mohun_2005, Section 2.1, Equations 1-3, 13-14; full_transcription.md</t>
+          <t>Mohun 2005, Figure 2 (L_p/L) and Table 2 (Services sector productive labour 1988), CJE 29(5):799-815 (~pp.806-811)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>trend_description</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Both ST and SM estimates show a declining trend in L_p/L from 1964 to 2001. SM estimates: start ~0.45 (1964), decline to ~0.38 (2001), with more volatility in the 1970s. ST estimates: start ~0.45 (1964), decline to ~0.36 (2001), smoother decline. The SM series is systematically higher than ST by an amount that widens over time: ST averages 96.4% of SM in 1989, 95.1% in 2001.</t>
+          <t>Productive labor share = L_p / L, where L_p is total productive full-time equivalent employment and L is total employment. Calculated using the SM (Simon Mohun) approximation: for each productive SIC division i, L_p^i = (L_pn^i / L^i)_BLS × (L^i)_NIPA, where BLS production worker ratios are applied to NIPA total employment. For Services divisions the SM approximation uses division-level BLS ratios weighted by a factor alpha^{s,j} = geometric mean of division BLS ratio / geometric mean of aggregate Services BLS ratio (first 5 years available).</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mohun_2005, Fig 2; full_transcription.md Section 4</t>
+          <t>Mohun_2005, Section 2.1, Equations 1-3, 13-14; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>st_vs_sm_comparison</t>
+          <t>trend_description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Figure 1 ST-to-SM ratio for productive workers L_p: 1964: ST = 99.7% of SM; 1989: ST = 96.4% of SM; 2001: ST = 95.1% of SM. The ST approximation systematically underestimates the productive labor share because its GDP-weighted services method is less accurate than SM's ratio-weighted method. The underestimate widens over time as the services sector grows (from 16.1% of employment in 1964 to 31.3% in 2001).</t>
+          <t>Both ST and SM estimates show a declining trend in L_p/L from 1964 to 2001. SM estimates: start ~0.45 (1964), decline to ~0.38 (2001), with more volatility in the 1970s. ST estimates: start ~0.45 (1964), decline to ~0.36 (2001), smoother decline. The SM series is systematically higher than ST by an amount that widens over time: ST averages 96.4% of SM in 1989, 95.1% in 2001.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mohun_2005, Fig 1 and Fig 2; full_transcription.md Section 4</t>
+          <t>Mohun_2005, Fig 2; full_transcription.md Section 4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>services_sector_note</t>
+          <t>st_vs_sm_comparison</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Services sector (SIC divisions 70-89) is the most important source of discrepancy between ST and SM. In 1988 benchmark year, ST productive services employment = 14,170 thousand (91.2% of benchmark), SM = 15,313 thousand (98.5% of benchmark). The SM approximation does not depend on problematic GDP contribution estimates for services; instead it exploits the empirical finding that individual Services division BLS production worker ratios are not very different from the aggregate Services BLS ratio.</t>
+          <t>Figure 1 ST-to-SM ratio for productive workers L_p: 1964: ST = 99.7% of SM; 1989: ST = 96.4% of SM; 2001: ST = 95.1% of SM. The ST approximation systematically underestimates the productive labor share because its GDP-weighted services method is less accurate than SM's ratio-weighted method. The underestimate widens over time as the services sector grows (from 16.1% of employment in 1964 to 31.3% in 2001).</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mohun_2005, Table 2; full_transcription.md Section 3.1.1</t>
+          <t>Mohun_2005, Fig 1 and Fig 2; full_transcription.md Section 4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>services_sector_note</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Services sector (SIC divisions 70-89) is the most important source of discrepancy between ST and SM. In 1988 benchmark year, ST productive services employment = 14,170 thousand (91.2% of benchmark), SM = 15,313 thousand (98.5% of benchmark). The SM approximation does not depend on problematic GDP contribution estimates for services; instead it exploits the empirical finding that individual Services division BLS production worker ratios are not very different from the aggregate Services BLS ratio.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Table 2; full_transcription.md Section 3.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>bls_production_worker_definition</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>BLS 'production workers' in private service-producing industries are nonsupervisory employees: employees not above working supervisory level, including office and clerical workers, repairers, salespersons, operators, drivers, physicians, lawyers, accountants, nurses, social workers, research aides, teachers, drafters, photographers, beauticians, musicians, restaurant workers, custodial workers, attendants, line installers, laborers, janitors, guards, and 'other employees at similar occupational levels whose services are closely associated with those of the employees listed.'</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Mohun_2005, Section 2.1; full_transcription.md</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Productive labor share (L_p/L) under Mohun SM approximation. Declines from ~0.45 (1964) to ~0.38 (2001). SM systematically higher than ST (ST = 95.1% of SM by 2001) due to superior services sector approximation. Loaded from Mohun 2005 Table 2 via L15.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Productive labor share (L_p/L) under Mohun SM approximation. Declines from ~0.45 (1964) to ~0.38 (2001). SM systematically higher than ST (ST = 95.1% of SM by 2001) due to superior services sector approximation. Data provenance: loaded (pass-through) from project reconstruction file Mohun_mohun_employment_annual_1948_1989.csv col Lp_mohun_L_ratio, a book-period 1948-1989 SM-classification reconstruction — NOT a transcription of a Mohun 2005 published table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Services sector data gaps prior to 1988 require approximation; no benchmark validation possible for 1964-1987</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1490,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agriculture sector uses Mining BLS ratio as proxy for Farms component — assessed by Mohun as having small net effect</t>
+          <t>Services sector data gaps prior to 1988 require approximation; no benchmark validation possible for 1964-1987</t>
         </is>
       </c>
     </row>
@@ -1489,23 +1498,23 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Agriculture sector uses Mining BLS ratio as proxy for Farms component — assessed by Mohun as having small net effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Government enterprises use Transportation/Public Utilities BLS ratio as proxy — very small sector weight</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>XS1401</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1522,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XS1403</t>
+          <t>XS1401</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1530,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XS1404</t>
+          <t>XS1403</t>
         </is>
       </c>
     </row>
@@ -1529,37 +1538,45 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
+          <t>XS1404</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>S505</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mohun_2005</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Mohun_2005</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>

--- a/extenbooks/XS1402.xlsx
+++ b/extenbooks/XS1402.xlsx
@@ -1102,7 +1102,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>`data/source/external_studies/Mohun_mohun_employment_annual_1948_1989.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_XS1402_productive_labor_share_mohun2005.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1402_productive_labor_share_mohun2005.py`.</t>
+          <t>`data/source/external_studies/Mohun_mohun_employment_annual_1948_1989.csv` (copied from predecessor-build's ExternalSources). Loader: `code/L01_loaders/L01_XS1402_productive_labor_share_mohun2005.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1402_productive_labor_share_mohun2005.py`.</t>
         </is>
       </c>
     </row>
